--- a/docs/journey/files/Travel History.xlsx
+++ b/docs/journey/files/Travel History.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lwyoh\myflightlog\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BF3256-EDBE-4621-88CC-3683C63916DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A221B04-8FFC-481E-B843-917217487570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="104">
   <si>
     <t>Country</t>
   </si>
@@ -325,6 +325,18 @@
   </si>
   <si>
     <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Ticino</t>
+  </si>
+  <si>
+    <t>2025-05</t>
+  </si>
+  <si>
+    <t>Nidwalden</t>
+  </si>
+  <si>
+    <t>Obwalden</t>
   </si>
 </sst>
 </file>
@@ -648,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.109375" customWidth="1"/>
@@ -1355,6 +1367,48 @@
         <v>97</v>
       </c>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/journey/files/Travel History.xlsx
+++ b/docs/journey/files/Travel History.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lwyoh\myflightlog\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lwyoh\wenyuliu_ch\journey\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A221B04-8FFC-481E-B843-917217487570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ABD1B6-C811-4D19-8C36-70B6FBA91721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="106">
   <si>
     <t>Country</t>
   </si>
@@ -337,6 +337,12 @@
   </si>
   <si>
     <t>Obwalden</t>
+  </si>
+  <si>
+    <t>Graubünden</t>
+  </si>
+  <si>
+    <t>2025-06</t>
   </si>
 </sst>
 </file>
@@ -660,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.109375" customWidth="1"/>
@@ -1409,6 +1415,20 @@
         <v>101</v>
       </c>
     </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/journey/files/Travel History.xlsx
+++ b/docs/journey/files/Travel History.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lwyoh\wenyuliu_ch\journey\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ABD1B6-C811-4D19-8C36-70B6FBA91721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAF8586-A879-4051-98AC-439532973170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="111">
   <si>
     <t>Country</t>
   </si>
@@ -343,6 +343,21 @@
   </si>
   <si>
     <t>2025-06</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>LIE</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>2025-07</t>
   </si>
 </sst>
 </file>
@@ -666,14 +681,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D56"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.1328125" customWidth="1"/>
+    <col min="3" max="3" width="23.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -687,7 +702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -701,7 +716,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -715,7 +730,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -729,7 +744,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -743,7 +758,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -757,7 +772,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -771,7 +786,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -785,7 +800,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -799,7 +814,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -813,7 +828,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -827,7 +842,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -841,7 +856,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -855,7 +870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -869,7 +884,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -883,7 +898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -897,7 +912,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -911,7 +926,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -925,7 +940,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -939,7 +954,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -953,7 +968,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -967,7 +982,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -981,7 +996,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -995,7 +1010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1009,7 +1024,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1023,7 +1038,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1037,7 +1052,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1051,7 +1066,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1065,7 +1080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1079,7 +1094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1093,7 +1108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1107,7 +1122,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1121,7 +1136,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1135,7 +1150,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1149,7 +1164,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1163,7 +1178,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1177,7 +1192,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1191,7 +1206,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1205,7 +1220,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -1219,7 +1234,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1233,7 +1248,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1247,7 +1262,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1261,7 +1276,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -1275,7 +1290,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -1289,7 +1304,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1303,7 +1318,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -1317,7 +1332,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -1331,7 +1346,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>20</v>
       </c>
@@ -1345,7 +1360,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -1359,7 +1374,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -1373,7 +1388,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -1387,7 +1402,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -1401,7 +1416,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -1415,7 +1430,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -1427,6 +1442,34 @@
       </c>
       <c r="D54" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/docs/journey/files/Travel History.xlsx
+++ b/docs/journey/files/Travel History.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lwyoh\wenyuliu_ch\journey\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAF8586-A879-4051-98AC-439532973170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646DCF2-CB07-4EFB-BD1C-EF1F733B6AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="114">
   <si>
     <t>Country</t>
   </si>
@@ -358,6 +358,15 @@
   </si>
   <si>
     <t>2025-07</t>
+  </si>
+  <si>
+    <t>Thurgau</t>
+  </si>
+  <si>
+    <t>Appenzell Innerrhoden</t>
+  </si>
+  <si>
+    <t>2025-08</t>
   </si>
 </sst>
 </file>
@@ -681,14 +690,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.1328125" customWidth="1"/>
-    <col min="3" max="3" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -702,7 +711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -716,7 +725,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -730,7 +739,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -744,7 +753,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -758,7 +767,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -772,7 +781,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -786,7 +795,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -800,7 +809,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -814,7 +823,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -828,7 +837,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -842,7 +851,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -856,7 +865,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -870,7 +879,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -884,7 +893,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -898,7 +907,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -912,7 +921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -926,7 +935,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -940,7 +949,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -954,7 +963,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -968,7 +977,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -982,7 +991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -996,7 +1005,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -1010,7 +1019,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1024,7 +1033,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1038,7 +1047,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1052,7 +1061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1066,7 +1075,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1080,7 +1089,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1094,7 +1103,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1108,7 +1117,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1122,7 +1131,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1136,7 +1145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1150,7 +1159,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1164,7 +1173,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1178,7 +1187,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1192,7 +1201,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1206,7 +1215,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1220,7 +1229,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -1234,7 +1243,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1248,7 +1257,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1262,7 +1271,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1276,7 +1285,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -1290,7 +1299,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -1304,7 +1313,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1318,7 +1327,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -1332,7 +1341,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -1346,7 +1355,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>20</v>
       </c>
@@ -1360,7 +1369,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -1374,7 +1383,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -1402,7 +1411,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -1416,7 +1425,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -1430,7 +1439,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -1444,7 +1453,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -1458,7 +1467,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -1470,6 +1479,34 @@
       </c>
       <c r="D56" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/docs/journey/files/Travel History.xlsx
+++ b/docs/journey/files/Travel History.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lwyoh\wenyuliu_ch\journey\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646DCF2-CB07-4EFB-BD1C-EF1F733B6AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504C97FF-700A-4DE0-88D2-D6F33E9AEC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="115">
   <si>
     <t>Country</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>2025-08</t>
+  </si>
+  <si>
+    <t>Neuchâtel</t>
   </si>
 </sst>
 </file>
@@ -690,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.109375" customWidth="1"/>
@@ -1509,6 +1512,20 @@
         <v>113</v>
       </c>
     </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
